--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/39.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/39.xlsx
@@ -426,13 +426,13 @@
         <v>-13.65183901609245</v>
       </c>
       <c r="E2">
-        <v>-19.15704115200391</v>
+        <v>-22.22101119406769</v>
       </c>
       <c r="F2">
-        <v>0.2602853814379324</v>
+        <v>-0.2566869079507973</v>
       </c>
       <c r="G2">
-        <v>-13.19571649056387</v>
+        <v>-15.58587574591627</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.25284445856536</v>
       </c>
       <c r="E3">
-        <v>-19.16255230487125</v>
+        <v>-20.1954066565407</v>
       </c>
       <c r="F3">
-        <v>0.1124179275251821</v>
+        <v>-0.6441754016931978</v>
       </c>
       <c r="G3">
-        <v>-12.06994230611593</v>
+        <v>-14.42249541941498</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.80914480842039</v>
       </c>
       <c r="E4">
-        <v>-17.95252140765169</v>
+        <v>-20.92589932719202</v>
       </c>
       <c r="F4">
-        <v>0.5061097973383589</v>
+        <v>-0.4903579646561415</v>
       </c>
       <c r="G4">
-        <v>-13.02714020115864</v>
+        <v>-15.00676201473156</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.35264045175329</v>
       </c>
       <c r="E5">
-        <v>-18.61173589742227</v>
+        <v>-22.53272870238568</v>
       </c>
       <c r="F5">
-        <v>0.2078259148419584</v>
+        <v>-0.4640605279302694</v>
       </c>
       <c r="G5">
-        <v>-12.25061201837612</v>
+        <v>-15.11821815140221</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.86743675040126</v>
       </c>
       <c r="E6">
-        <v>-18.42203812124096</v>
+        <v>-22.1463321292072</v>
       </c>
       <c r="F6">
-        <v>0.2948671838074682</v>
+        <v>-1.075388432054966</v>
       </c>
       <c r="G6">
-        <v>-12.45266454427445</v>
+        <v>-15.60664610862966</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.36553298677036</v>
       </c>
       <c r="E7">
-        <v>-19.49341620129367</v>
+        <v>-22.08519773010364</v>
       </c>
       <c r="F7">
-        <v>0.5151852240867847</v>
+        <v>-0.398888653951063</v>
       </c>
       <c r="G7">
-        <v>-12.31305883888339</v>
+        <v>-15.23304276815906</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.8470136448885</v>
       </c>
       <c r="E8">
-        <v>-21.1140438367887</v>
+        <v>-23.41890578094669</v>
       </c>
       <c r="F8">
-        <v>0.7270811163077942</v>
+        <v>-1.121501197194816</v>
       </c>
       <c r="G8">
-        <v>-12.24494767495842</v>
+        <v>-14.31588261086829</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.30209962129461</v>
       </c>
       <c r="E9">
-        <v>-22.08075529710212</v>
+        <v>-24.51088841773429</v>
       </c>
       <c r="F9">
-        <v>0.411389930241841</v>
+        <v>0.4686456502027233</v>
       </c>
       <c r="G9">
-        <v>-12.90579215441666</v>
+        <v>-15.32170414351905</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.724249200899013</v>
       </c>
       <c r="E10">
-        <v>-22.16010321866452</v>
+        <v>-25.17176485746569</v>
       </c>
       <c r="F10">
-        <v>0.607728287402531</v>
+        <v>-0.6073241487468373</v>
       </c>
       <c r="G10">
-        <v>-12.34611463609301</v>
+        <v>-15.05497679996551</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.120673517566395</v>
       </c>
       <c r="E11">
-        <v>-21.56621196645458</v>
+        <v>-24.45379794591959</v>
       </c>
       <c r="F11">
-        <v>0.955500604197541</v>
+        <v>-0.04088163767752555</v>
       </c>
       <c r="G11">
-        <v>-11.44348115262856</v>
+        <v>-14.40836601105337</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.488934650920289</v>
       </c>
       <c r="E12">
-        <v>-22.69295969819908</v>
+        <v>-27.20420739074425</v>
       </c>
       <c r="F12">
-        <v>0.8925245384700914</v>
+        <v>0.03788555973277081</v>
       </c>
       <c r="G12">
-        <v>-10.98168322371901</v>
+        <v>-15.21810724195863</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.826817002703976</v>
       </c>
       <c r="E13">
-        <v>-22.27381320099712</v>
+        <v>-25.83037253171925</v>
       </c>
       <c r="F13">
-        <v>1.261851092774232</v>
+        <v>0.1312616523600383</v>
       </c>
       <c r="G13">
-        <v>-10.81807937371377</v>
+        <v>-14.73429915103123</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.156764859514958</v>
       </c>
       <c r="E14">
-        <v>-23.86741943208838</v>
+        <v>-25.84348246397145</v>
       </c>
       <c r="F14">
-        <v>1.06961453393453</v>
+        <v>-0.1206917054331388</v>
       </c>
       <c r="G14">
-        <v>-10.30829839775801</v>
+        <v>-12.36314408234702</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.488249509861536</v>
       </c>
       <c r="E15">
-        <v>-24.48455534137969</v>
+        <v>-27.04956000338231</v>
       </c>
       <c r="F15">
-        <v>1.669603103704681</v>
+        <v>0.8528938816421346</v>
       </c>
       <c r="G15">
-        <v>-10.51285369608404</v>
+        <v>-11.62295575794907</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.825070175238875</v>
       </c>
       <c r="E16">
-        <v>-26.45421511101591</v>
+        <v>-27.91189919476695</v>
       </c>
       <c r="F16">
-        <v>1.582762173537474</v>
+        <v>0.6986235047132626</v>
       </c>
       <c r="G16">
-        <v>-9.516250377487383</v>
+        <v>-13.37539966025335</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.184257813295146</v>
       </c>
       <c r="E17">
-        <v>-26.04881253242724</v>
+        <v>-28.15678095520573</v>
       </c>
       <c r="F17">
-        <v>2.093865248803585</v>
+        <v>0.657017966608753</v>
       </c>
       <c r="G17">
-        <v>-9.814434524755077</v>
+        <v>-13.02526974292896</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.573088737018963</v>
       </c>
       <c r="E18">
-        <v>-25.50792254000308</v>
+        <v>-31.16169743197247</v>
       </c>
       <c r="F18">
-        <v>1.815882100584245</v>
+        <v>0.4914708117089944</v>
       </c>
       <c r="G18">
-        <v>-8.024419241125607</v>
+        <v>-12.54856442745606</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.990459871835006</v>
       </c>
       <c r="E19">
-        <v>-28.28536697465353</v>
+        <v>-30.51638309316844</v>
       </c>
       <c r="F19">
-        <v>2.486822279071998</v>
+        <v>0.7945184815990366</v>
       </c>
       <c r="G19">
-        <v>-7.931896114394056</v>
+        <v>-12.03926017005796</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.441727963103362</v>
       </c>
       <c r="E20">
-        <v>-28.82293759563007</v>
+        <v>-31.24849242904049</v>
       </c>
       <c r="F20">
-        <v>2.773321013998656</v>
+        <v>1.235772207464691</v>
       </c>
       <c r="G20">
-        <v>-7.663722062439854</v>
+        <v>-12.40186422297434</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.931276421963747</v>
       </c>
       <c r="E21">
-        <v>-29.19888245079885</v>
+        <v>-31.47968008408008</v>
       </c>
       <c r="F21">
-        <v>2.489025214000374</v>
+        <v>1.931671591179769</v>
       </c>
       <c r="G21">
-        <v>-8.103670390790221</v>
+        <v>-10.96557741967045</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.457196562153844</v>
       </c>
       <c r="E22">
-        <v>-30.11598674259524</v>
+        <v>-32.73430286485316</v>
       </c>
       <c r="F22">
-        <v>2.649663672415228</v>
+        <v>1.828022790132004</v>
       </c>
       <c r="G22">
-        <v>-6.922576990381057</v>
+        <v>-10.72498683314946</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.019734026530632</v>
       </c>
       <c r="E23">
-        <v>-30.13807437456765</v>
+        <v>-33.28779333620367</v>
       </c>
       <c r="F23">
-        <v>2.392186348388998</v>
+        <v>2.082500575154392</v>
       </c>
       <c r="G23">
-        <v>-6.834430404852422</v>
+        <v>-9.676010684121531</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.624958204150849</v>
       </c>
       <c r="E24">
-        <v>-30.0716846813782</v>
+        <v>-34.57434638720484</v>
       </c>
       <c r="F24">
-        <v>3.081731903971334</v>
+        <v>1.877667219463284</v>
       </c>
       <c r="G24">
-        <v>-6.421314048097849</v>
+        <v>-9.853727389760687</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.271590913315827</v>
       </c>
       <c r="E25">
-        <v>-31.64982843797027</v>
+        <v>-35.87105906964222</v>
       </c>
       <c r="F25">
-        <v>2.705506726699539</v>
+        <v>2.398841080645675</v>
       </c>
       <c r="G25">
-        <v>-6.578677519761565</v>
+        <v>-11.60811127175098</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.9546614206032746</v>
       </c>
       <c r="E26">
-        <v>-31.17650554197756</v>
+        <v>-35.03431934182294</v>
       </c>
       <c r="F26">
-        <v>2.646725897942088</v>
+        <v>1.88428394277799</v>
       </c>
       <c r="G26">
-        <v>-6.262199297843858</v>
+        <v>-10.46029878564811</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.6758992181396857</v>
       </c>
       <c r="E27">
-        <v>-32.0383171661403</v>
+        <v>-34.05863923873734</v>
       </c>
       <c r="F27">
-        <v>3.087205191615092</v>
+        <v>1.985468497421332</v>
       </c>
       <c r="G27">
-        <v>-5.935468316391027</v>
+        <v>-9.697433224306154</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.4304082164713626</v>
       </c>
       <c r="E28">
-        <v>-32.36626472530178</v>
+        <v>-34.35845138888916</v>
       </c>
       <c r="F28">
-        <v>2.985227200308116</v>
+        <v>1.691922271170969</v>
       </c>
       <c r="G28">
-        <v>-5.842965052932712</v>
+        <v>-10.69422524399855</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.2123993893142821</v>
       </c>
       <c r="E29">
-        <v>-30.8941483948883</v>
+        <v>-35.91538830170331</v>
       </c>
       <c r="F29">
-        <v>2.782088409946529</v>
+        <v>1.257766715218314</v>
       </c>
       <c r="G29">
-        <v>-5.8442031969644</v>
+        <v>-9.370324840661848</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.02031518748913933</v>
       </c>
       <c r="E30">
-        <v>-31.84722688420163</v>
+        <v>-35.48067517509999</v>
       </c>
       <c r="F30">
-        <v>2.808761184974359</v>
+        <v>2.303679359598749</v>
       </c>
       <c r="G30">
-        <v>-5.539050351336538</v>
+        <v>-8.292854826177411</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.1489443160614002</v>
       </c>
       <c r="E31">
-        <v>-30.71571972627508</v>
+        <v>-35.15013959304312</v>
       </c>
       <c r="F31">
-        <v>3.051519546222495</v>
+        <v>2.35777558625833</v>
       </c>
       <c r="G31">
-        <v>-5.610068174244984</v>
+        <v>-10.06248708092159</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.2984720752742379</v>
       </c>
       <c r="E32">
-        <v>-30.78055388864289</v>
+        <v>-34.01262088587139</v>
       </c>
       <c r="F32">
-        <v>2.470874360503523</v>
+        <v>1.831069840313309</v>
       </c>
       <c r="G32">
-        <v>-6.772102763984563</v>
+        <v>-10.04522589647983</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.4288572211379352</v>
       </c>
       <c r="E33">
-        <v>-31.45545274813904</v>
+        <v>-33.50627182894073</v>
       </c>
       <c r="F33">
-        <v>2.569618424331172</v>
+        <v>2.161850576341569</v>
       </c>
       <c r="G33">
-        <v>-5.677977394892054</v>
+        <v>-10.01049165268179</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.5388838439498823</v>
       </c>
       <c r="E34">
-        <v>-30.42635702989595</v>
+        <v>-34.41824535968644</v>
       </c>
       <c r="F34">
-        <v>2.830540308723483</v>
+        <v>1.862487398263797</v>
       </c>
       <c r="G34">
-        <v>-6.091477774929182</v>
+        <v>-9.645590081161169</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.6272298262382184</v>
       </c>
       <c r="E35">
-        <v>-30.44609664809539</v>
+        <v>-34.30422970535832</v>
       </c>
       <c r="F35">
-        <v>3.053941032567202</v>
+        <v>1.799706128363947</v>
       </c>
       <c r="G35">
-        <v>-6.452366965256212</v>
+        <v>-10.88007264948216</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.6916205588705343</v>
       </c>
       <c r="E36">
-        <v>-29.73063398267553</v>
+        <v>-34.8931305792118</v>
       </c>
       <c r="F36">
-        <v>2.88516232574699</v>
+        <v>1.319794141102415</v>
       </c>
       <c r="G36">
-        <v>-6.558039578869749</v>
+        <v>-11.21180586524483</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.7291767872144911</v>
       </c>
       <c r="E37">
-        <v>-29.7353979373316</v>
+        <v>-33.38023307612224</v>
       </c>
       <c r="F37">
-        <v>2.624538178066781</v>
+        <v>1.282056012843409</v>
       </c>
       <c r="G37">
-        <v>-6.463202380806247</v>
+        <v>-10.78335837209789</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.7388557038395496</v>
       </c>
       <c r="E38">
-        <v>-29.98819547033579</v>
+        <v>-33.67368045605629</v>
       </c>
       <c r="F38">
-        <v>2.668319728099105</v>
+        <v>1.755748786975009</v>
       </c>
       <c r="G38">
-        <v>-7.194919019169201</v>
+        <v>-11.23536370730228</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.7212134032722032</v>
       </c>
       <c r="E39">
-        <v>-29.02000319902186</v>
+        <v>-31.60047486399768</v>
       </c>
       <c r="F39">
-        <v>3.091337080348474</v>
+        <v>1.365930661830997</v>
       </c>
       <c r="G39">
-        <v>-7.178574855841819</v>
+        <v>-10.54509178854546</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.6774213645603167</v>
       </c>
       <c r="E40">
-        <v>-28.16423482342235</v>
+        <v>-31.4190619310134</v>
       </c>
       <c r="F40">
-        <v>2.765698637427646</v>
+        <v>1.712868365608571</v>
       </c>
       <c r="G40">
-        <v>-7.160813779023629</v>
+        <v>-10.17154969316734</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.6099984207346634</v>
       </c>
       <c r="E41">
-        <v>-28.83886876718906</v>
+        <v>-30.99109623068151</v>
       </c>
       <c r="F41">
-        <v>2.775395668747881</v>
+        <v>1.491608812162525</v>
       </c>
       <c r="G41">
-        <v>-7.996385541499059</v>
+        <v>-11.26015638284588</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.5224901237611534</v>
       </c>
       <c r="E42">
-        <v>-27.8713693523983</v>
+        <v>-29.86438699096608</v>
       </c>
       <c r="F42">
-        <v>2.996720154136459</v>
+        <v>1.663379139457003</v>
       </c>
       <c r="G42">
-        <v>-8.368788809211674</v>
+        <v>-10.83592652471598</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.418725770737065</v>
       </c>
       <c r="E43">
-        <v>-26.55473817703818</v>
+        <v>-30.80372835437715</v>
       </c>
       <c r="F43">
-        <v>3.544245298045847</v>
+        <v>2.166091740783116</v>
       </c>
       <c r="G43">
-        <v>-8.221247726162975</v>
+        <v>-10.96581908949482</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.3032426602514299</v>
       </c>
       <c r="E44">
-        <v>-25.75545798621035</v>
+        <v>-29.69438581248113</v>
       </c>
       <c r="F44">
-        <v>3.317518791779705</v>
+        <v>1.959483050760802</v>
       </c>
       <c r="G44">
-        <v>-8.591962615650562</v>
+        <v>-11.24468289299533</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.1811615776387011</v>
       </c>
       <c r="E45">
-        <v>-25.37541486206463</v>
+        <v>-28.61868530398811</v>
       </c>
       <c r="F45">
-        <v>3.594160541088668</v>
+        <v>2.476105341142219</v>
       </c>
       <c r="G45">
-        <v>-8.22668033139292</v>
+        <v>-11.04697049229898</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.05685958566263667</v>
       </c>
       <c r="E46">
-        <v>-24.93618005416466</v>
+        <v>-27.91106142707553</v>
       </c>
       <c r="F46">
-        <v>3.829418471121282</v>
+        <v>2.722077041692781</v>
       </c>
       <c r="G46">
-        <v>-9.330624778554908</v>
+        <v>-12.20574088413683</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.06596773718477132</v>
       </c>
       <c r="E47">
-        <v>-25.08440153690971</v>
+        <v>-29.17992173012873</v>
       </c>
       <c r="F47">
-        <v>3.30079644101858</v>
+        <v>2.498980389384827</v>
       </c>
       <c r="G47">
-        <v>-8.574602114842625</v>
+        <v>-12.55277544138201</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.1849674382849451</v>
       </c>
       <c r="E48">
-        <v>-23.03471457460994</v>
+        <v>-26.94984753420742</v>
       </c>
       <c r="F48">
-        <v>3.657720994298914</v>
+        <v>1.897880058062038</v>
       </c>
       <c r="G48">
-        <v>-8.718494976707047</v>
+        <v>-13.48151588696915</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.299453759486824</v>
       </c>
       <c r="E49">
-        <v>-23.08944571146665</v>
+        <v>-27.65670157053869</v>
       </c>
       <c r="F49">
-        <v>3.346231380026622</v>
+        <v>1.807021265987361</v>
       </c>
       <c r="G49">
-        <v>-8.13178685405525</v>
+        <v>-11.36286936874731</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.4096456408877656</v>
       </c>
       <c r="E50">
-        <v>-23.20026652738235</v>
+        <v>-24.82347992153576</v>
       </c>
       <c r="F50">
-        <v>3.530688775409685</v>
+        <v>2.603501812391999</v>
       </c>
       <c r="G50">
-        <v>-8.201612880569558</v>
+        <v>-12.8381875039592</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.5162620046010035</v>
       </c>
       <c r="E51">
-        <v>-21.56940454062999</v>
+        <v>-27.17017590857661</v>
       </c>
       <c r="F51">
-        <v>3.699139655105402</v>
+        <v>1.985986369255681</v>
       </c>
       <c r="G51">
-        <v>-8.964918744468237</v>
+        <v>-12.43071562734909</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.620208712216145</v>
       </c>
       <c r="E52">
-        <v>-22.06696156527476</v>
+        <v>-25.89193713585352</v>
       </c>
       <c r="F52">
-        <v>3.862342133397353</v>
+        <v>2.677275585050915</v>
       </c>
       <c r="G52">
-        <v>-9.579978379118353</v>
+        <v>-13.51581479402877</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.7234565820190451</v>
       </c>
       <c r="E53">
-        <v>-21.42041774577763</v>
+        <v>-25.59866410216878</v>
       </c>
       <c r="F53">
-        <v>3.845679963461014</v>
+        <v>2.895027229894262</v>
       </c>
       <c r="G53">
-        <v>-9.223343239809285</v>
+        <v>-12.39019454994841</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.8279942253326621</v>
       </c>
       <c r="E54">
-        <v>-21.59508098825348</v>
+        <v>-24.93669177172752</v>
       </c>
       <c r="F54">
-        <v>3.828024809915695</v>
+        <v>2.625973015626169</v>
       </c>
       <c r="G54">
-        <v>-9.513846921425872</v>
+        <v>-12.9514942355863</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.9340727583642789</v>
       </c>
       <c r="E55">
-        <v>-21.31628095749725</v>
+        <v>-25.07098366842499</v>
       </c>
       <c r="F55">
-        <v>3.567460843060274</v>
+        <v>2.002357137303578</v>
       </c>
       <c r="G55">
-        <v>-8.966077435406982</v>
+        <v>-12.59892775674499</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.043670873485647</v>
       </c>
       <c r="E56">
-        <v>-20.03112267649044</v>
+        <v>-23.71376378053412</v>
       </c>
       <c r="F56">
-        <v>3.791244823735529</v>
+        <v>2.678151374422153</v>
       </c>
       <c r="G56">
-        <v>-9.215474073062438</v>
+        <v>-13.3402251138986</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.157623735740726</v>
       </c>
       <c r="E57">
-        <v>-18.9864082513949</v>
+        <v>-24.42579839113017</v>
       </c>
       <c r="F57">
-        <v>3.649691605307636</v>
+        <v>2.714836338247392</v>
       </c>
       <c r="G57">
-        <v>-10.04737775108035</v>
+        <v>-14.10760791462889</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.274310984079672</v>
       </c>
       <c r="E58">
-        <v>-19.0179400159103</v>
+        <v>-21.01860171860304</v>
       </c>
       <c r="F58">
-        <v>3.676491076808703</v>
+        <v>2.165067083055827</v>
       </c>
       <c r="G58">
-        <v>-9.270783357387041</v>
+        <v>-13.58365945903783</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.393998663515565</v>
       </c>
       <c r="E59">
-        <v>-19.42606420737759</v>
+        <v>-23.60983983053209</v>
       </c>
       <c r="F59">
-        <v>3.634885538704193</v>
+        <v>2.268758644163309</v>
       </c>
       <c r="G59">
-        <v>-10.53008177507041</v>
+        <v>-12.61076957813897</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.51700164016384</v>
       </c>
       <c r="E60">
-        <v>-19.68579936256153</v>
+        <v>-21.69983364899891</v>
       </c>
       <c r="F60">
-        <v>3.783133082036649</v>
+        <v>2.574700536613817</v>
       </c>
       <c r="G60">
-        <v>-8.758880321740616</v>
+        <v>-14.4900967593269</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.641542939768976</v>
       </c>
       <c r="E61">
-        <v>-17.87632077552462</v>
+        <v>-21.26327064076346</v>
       </c>
       <c r="F61">
-        <v>3.312750253268317</v>
+        <v>2.488583360049966</v>
       </c>
       <c r="G61">
-        <v>-9.760022398271616</v>
+        <v>-12.55746317386562</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.766442726862599</v>
       </c>
       <c r="E62">
-        <v>-18.88718032893882</v>
+        <v>-21.26366914647613</v>
       </c>
       <c r="F62">
-        <v>3.60409829570805</v>
+        <v>2.641599441893811</v>
       </c>
       <c r="G62">
-        <v>-10.14348950917648</v>
+        <v>-14.3737211519849</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.892874632216056</v>
       </c>
       <c r="E63">
-        <v>-18.31563709595674</v>
+        <v>-21.39787047369344</v>
       </c>
       <c r="F63">
-        <v>3.115490179264841</v>
+        <v>1.685467085859637</v>
       </c>
       <c r="G63">
-        <v>-9.912880217456385</v>
+        <v>-13.10603712245056</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.020067275446094</v>
       </c>
       <c r="E64">
-        <v>-17.79403387433124</v>
+        <v>-20.5475679662212</v>
       </c>
       <c r="F64">
-        <v>2.833112247130157</v>
+        <v>2.250555528371248</v>
       </c>
       <c r="G64">
-        <v>-9.642332504350525</v>
+        <v>-14.36158138149239</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.145619688188859</v>
       </c>
       <c r="E65">
-        <v>-16.854583827544</v>
+        <v>-21.61884189137173</v>
       </c>
       <c r="F65">
-        <v>3.131436514127401</v>
+        <v>1.728353842049738</v>
       </c>
       <c r="G65">
-        <v>-9.878314811480854</v>
+        <v>-13.24231241902911</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.271747602007375</v>
       </c>
       <c r="E66">
-        <v>-17.06867196473062</v>
+        <v>-22.80798746646791</v>
       </c>
       <c r="F66">
-        <v>2.480458948703762</v>
+        <v>1.431279119019775</v>
       </c>
       <c r="G66">
-        <v>-10.19191616932494</v>
+        <v>-13.50948668623046</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.398969731034656</v>
       </c>
       <c r="E67">
-        <v>-17.69999105461395</v>
+        <v>-21.61084460627418</v>
       </c>
       <c r="F67">
-        <v>2.861763070846372</v>
+        <v>1.69758560352458</v>
       </c>
       <c r="G67">
-        <v>-9.5275227850486</v>
+        <v>-14.12646809256612</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.524117618017734</v>
       </c>
       <c r="E68">
-        <v>-16.7242317032332</v>
+        <v>-20.29214391829256</v>
       </c>
       <c r="F68">
-        <v>2.311642232941579</v>
+        <v>0.630745869177528</v>
       </c>
       <c r="G68">
-        <v>-10.6679527545989</v>
+        <v>-14.10677365715299</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.649554967148593</v>
       </c>
       <c r="E69">
-        <v>-16.46708230670765</v>
+        <v>-20.46812494670463</v>
       </c>
       <c r="F69">
-        <v>2.214443866087398</v>
+        <v>1.452383584048921</v>
       </c>
       <c r="G69">
-        <v>-9.654260399928519</v>
+        <v>-14.02678591110589</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.775718283820763</v>
       </c>
       <c r="E70">
-        <v>-16.76333507628944</v>
+        <v>-21.86251454925046</v>
       </c>
       <c r="F70">
-        <v>2.120319472415086</v>
+        <v>1.539709128226252</v>
       </c>
       <c r="G70">
-        <v>-10.25836543938919</v>
+        <v>-12.64129611855659</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.89875769515029</v>
       </c>
       <c r="E71">
-        <v>-17.1112849051428</v>
+        <v>-20.7167155273557</v>
       </c>
       <c r="F71">
-        <v>1.709789641308957</v>
+        <v>1.266803341171811</v>
       </c>
       <c r="G71">
-        <v>-10.08854107431565</v>
+        <v>-11.57657501494388</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.017989251350139</v>
       </c>
       <c r="E72">
-        <v>-16.83498912051281</v>
+        <v>-22.2578593870681</v>
       </c>
       <c r="F72">
-        <v>1.843041073328116</v>
+        <v>1.309167474409817</v>
       </c>
       <c r="G72">
-        <v>-9.266827255467613</v>
+        <v>-13.69099562178485</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.133274396223305</v>
       </c>
       <c r="E73">
-        <v>-16.69148177920973</v>
+        <v>-19.84540090048786</v>
       </c>
       <c r="F73">
-        <v>1.629950274993908</v>
+        <v>1.073314070952997</v>
       </c>
       <c r="G73">
-        <v>-9.335226436854494</v>
+        <v>-13.64443445404777</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.240727134023687</v>
       </c>
       <c r="E74">
-        <v>-17.47315526309574</v>
+        <v>-21.05284603904904</v>
       </c>
       <c r="F74">
-        <v>2.056352006784571</v>
+        <v>0.4714290133491081</v>
       </c>
       <c r="G74">
-        <v>-9.696443371189913</v>
+        <v>-13.03981296948297</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.336452295201798</v>
       </c>
       <c r="E75">
-        <v>-16.86581897155703</v>
+        <v>-21.39416165348116</v>
       </c>
       <c r="F75">
-        <v>1.727305428733717</v>
+        <v>0.4174008860438914</v>
       </c>
       <c r="G75">
-        <v>-9.021628389555953</v>
+        <v>-12.1390996024313</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.42102915381555</v>
       </c>
       <c r="E76">
-        <v>-17.50809244006491</v>
+        <v>-20.97226184408255</v>
       </c>
       <c r="F76">
-        <v>1.895529838483526</v>
+        <v>0.7996607747064686</v>
       </c>
       <c r="G76">
-        <v>-8.733180556719255</v>
+        <v>-12.32204697002251</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.4915549455533</v>
       </c>
       <c r="E77">
-        <v>-18.56380652852509</v>
+        <v>-21.44527001113173</v>
       </c>
       <c r="F77">
-        <v>1.593805354885833</v>
+        <v>0.2499580351633518</v>
       </c>
       <c r="G77">
-        <v>-8.716197458102792</v>
+        <v>-10.56625610617802</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.542911745583559</v>
       </c>
       <c r="E78">
-        <v>-18.14043043659997</v>
+        <v>-21.73041896244672</v>
       </c>
       <c r="F78">
-        <v>1.255039573631927</v>
+        <v>-0.02725543198108454</v>
       </c>
       <c r="G78">
-        <v>-8.669141363807592</v>
+        <v>-13.39885156485355</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.5774260996882</v>
       </c>
       <c r="E79">
-        <v>-17.65073031435852</v>
+        <v>-22.0933761541615</v>
       </c>
       <c r="F79">
-        <v>1.415882330109873</v>
+        <v>0.5330518023718147</v>
       </c>
       <c r="G79">
-        <v>-8.134961667227412</v>
+        <v>-10.68727309836608</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.595715019280046</v>
       </c>
       <c r="E80">
-        <v>-18.73432621728392</v>
+        <v>-22.27350073629059</v>
       </c>
       <c r="F80">
-        <v>1.325002949858296</v>
+        <v>0.3529931501688845</v>
       </c>
       <c r="G80">
-        <v>-7.617384356526675</v>
+        <v>-10.90064437946319</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.595353908716584</v>
       </c>
       <c r="E81">
-        <v>-19.57602009566758</v>
+        <v>-22.64942747756334</v>
       </c>
       <c r="F81">
-        <v>1.284309626361079</v>
+        <v>0.2674065150867059</v>
       </c>
       <c r="G81">
-        <v>-7.903892209677361</v>
+        <v>-10.11308214839827</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.581821221774663</v>
       </c>
       <c r="E82">
-        <v>-19.99615380020321</v>
+        <v>-21.92407915338474</v>
       </c>
       <c r="F82">
-        <v>1.230538059414163</v>
+        <v>0.04168645392982549</v>
       </c>
       <c r="G82">
-        <v>-7.436069087886332</v>
+        <v>-10.91238026339991</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.559392892190036</v>
       </c>
       <c r="E83">
-        <v>-21.53940340032917</v>
+        <v>-23.82422231852922</v>
       </c>
       <c r="F83">
-        <v>1.331393203227094</v>
+        <v>-0.2244965015135751</v>
       </c>
       <c r="G83">
-        <v>-7.426617480371712</v>
+        <v>-9.583004217741246</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.528095469002582</v>
       </c>
       <c r="E84">
-        <v>-21.99207419060991</v>
+        <v>-25.29176941866896</v>
       </c>
       <c r="F84">
-        <v>1.571015826762659</v>
+        <v>0.3354464804787731</v>
       </c>
       <c r="G84">
-        <v>-6.678235555764068</v>
+        <v>-9.313618506119671</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.490907820732381</v>
       </c>
       <c r="E85">
-        <v>-22.25991078579357</v>
+        <v>-27.37417007720014</v>
       </c>
       <c r="F85">
-        <v>0.8566979432510202</v>
+        <v>-0.368228899281113</v>
       </c>
       <c r="G85">
-        <v>-6.263523516059567</v>
+        <v>-9.375916352077677</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.45191784819952</v>
       </c>
       <c r="E86">
-        <v>-23.40679211297617</v>
+        <v>-29.72580210090935</v>
       </c>
       <c r="F86">
-        <v>1.169579635022984</v>
+        <v>0.4687778896466625</v>
       </c>
       <c r="G86">
-        <v>-6.626269922434128</v>
+        <v>-9.233731731711519</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.410537025881814</v>
       </c>
       <c r="E87">
-        <v>-24.86163684352439</v>
+        <v>-28.59656823693464</v>
       </c>
       <c r="F87">
-        <v>1.208426357422798</v>
+        <v>0.227137624774827</v>
       </c>
       <c r="G87">
-        <v>-6.685293638853794</v>
+        <v>-8.518180487216826</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.365250628057883</v>
       </c>
       <c r="E88">
-        <v>-26.0455429741937</v>
+        <v>-30.25717324096939</v>
       </c>
       <c r="F88">
-        <v>1.118125029830356</v>
+        <v>0.1072289150932447</v>
       </c>
       <c r="G88">
-        <v>-6.691775687019687</v>
+        <v>-9.072829286866321</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.320021964950133</v>
       </c>
       <c r="E89">
-        <v>-27.36666186729542</v>
+        <v>-30.650733860028</v>
       </c>
       <c r="F89">
-        <v>0.6384490147502254</v>
+        <v>-0.4485536714592441</v>
       </c>
       <c r="G89">
-        <v>-5.563826474152444</v>
+        <v>-9.349594204494931</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.273465708218072</v>
       </c>
       <c r="E90">
-        <v>-27.94150182935509</v>
+        <v>-30.62990967230373</v>
       </c>
       <c r="F90">
-        <v>0.5100183835376635</v>
+        <v>-0.04385425368080539</v>
       </c>
       <c r="G90">
-        <v>-5.076246016583045</v>
+        <v>-9.284594953376882</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.220795354088164</v>
       </c>
       <c r="E91">
-        <v>-27.84127311414332</v>
+        <v>-32.97565694403997</v>
       </c>
       <c r="F91">
-        <v>0.7721676400144397</v>
+        <v>-0.3731043379417934</v>
       </c>
       <c r="G91">
-        <v>-5.792091899630732</v>
+        <v>-9.072097656302143</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.161677317704821</v>
       </c>
       <c r="E92">
-        <v>-31.09383824896754</v>
+        <v>-35.79805554016457</v>
       </c>
       <c r="F92">
-        <v>0.6738400908425508</v>
+        <v>-1.229232792092585</v>
       </c>
       <c r="G92">
-        <v>-6.813209807945694</v>
+        <v>-8.164713539988842</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.09068348829715</v>
       </c>
       <c r="E93">
-        <v>-32.25746360879349</v>
+        <v>-34.73043835777523</v>
       </c>
       <c r="F93">
-        <v>0.5665646032484289</v>
+        <v>-0.7586599186144</v>
       </c>
       <c r="G93">
-        <v>-6.112095852547763</v>
+        <v>-8.561373174867697</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.998474107171925</v>
       </c>
       <c r="E94">
-        <v>-33.75169474202343</v>
+        <v>-37.97542282711061</v>
       </c>
       <c r="F94">
-        <v>0.3304593905510543</v>
+        <v>-0.6177512684940906</v>
       </c>
       <c r="G94">
-        <v>-5.862566793070736</v>
+        <v>-8.464695313484361</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.879648844107293</v>
       </c>
       <c r="E95">
-        <v>-35.3821469018781</v>
+        <v>-38.70960393984117</v>
       </c>
       <c r="F95">
-        <v>0.2466108727110705</v>
+        <v>-0.8828256297966836</v>
       </c>
       <c r="G95">
-        <v>-6.040826428178333</v>
+        <v>-8.935832291360201</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.72604935840945</v>
       </c>
       <c r="E96">
-        <v>-37.29038697854829</v>
+        <v>-41.00635312281442</v>
       </c>
       <c r="F96">
-        <v>0.07401701834056408</v>
+        <v>-0.5780738923416284</v>
       </c>
       <c r="G96">
-        <v>-5.491606923213243</v>
+        <v>-7.111926953045211</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.533263438891949</v>
       </c>
       <c r="E97">
-        <v>-39.50174046292189</v>
+        <v>-40.91310731452248</v>
       </c>
       <c r="F97">
-        <v>-0.113455753105496</v>
+        <v>-0.70487251460833</v>
       </c>
       <c r="G97">
-        <v>-7.046990602292407</v>
+        <v>-8.557049602393409</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.293499896276509</v>
       </c>
       <c r="E98">
-        <v>-42.16981092910208</v>
+        <v>-42.90064549954098</v>
       </c>
       <c r="F98">
-        <v>0.1491797010873203</v>
+        <v>-1.758249164968231</v>
       </c>
       <c r="G98">
-        <v>-4.58177962429196</v>
+        <v>-8.791479263665821</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.017182779242535</v>
       </c>
       <c r="E99">
-        <v>-43.97964273711159</v>
+        <v>-46.26449788310369</v>
       </c>
       <c r="F99">
-        <v>-0.2335014533487638</v>
+        <v>-1.228681662434012</v>
       </c>
       <c r="G99">
-        <v>-5.620185201412997</v>
+        <v>-11.03705540840886</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.696686977860834</v>
       </c>
       <c r="E100">
-        <v>-44.98781690543925</v>
+        <v>-47.83137932483869</v>
       </c>
       <c r="F100">
-        <v>-0.6136177960547936</v>
+        <v>-1.756568061138992</v>
       </c>
       <c r="G100">
-        <v>-5.323480868001356</v>
+        <v>-9.901197302248297</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.357855786387817</v>
       </c>
       <c r="E101">
-        <v>-47.69781424821945</v>
+        <v>-50.62856224557007</v>
       </c>
       <c r="F101">
-        <v>-0.5065703621124951</v>
+        <v>-2.307826791744028</v>
       </c>
       <c r="G101">
-        <v>-6.10288922540305</v>
+        <v>-8.498711168900373</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.982538503847826</v>
       </c>
       <c r="E102">
-        <v>-49.37913362448379</v>
+        <v>-49.65647435449105</v>
       </c>
       <c r="F102">
-        <v>-0.5293551391179224</v>
+        <v>-1.743119230505081</v>
       </c>
       <c r="G102">
-        <v>-7.033556408494045</v>
+        <v>-9.108003833221078</v>
       </c>
     </row>
   </sheetData>
